--- a/Bulk density/bulk density & MC data.xlsx
+++ b/Bulk density/bulk density & MC data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/haninhn_student_unimelb_edu_au/Documents/Documents/Chapter 2/Chapter 2 data/Bulk density/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/firecaster/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="14_{14B37A37-1BBD-F74C-AF27-1D0FDC2FB7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF6BC259-A44C-4D29-8795-BA84D729B69D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8B9858-A8F8-A949-8D83-FE39CF940CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="864" yWindow="-108" windowWidth="22284" windowHeight="14616" tabRatio="783" xr2:uid="{4CDCF8AC-F2BC-480F-9220-6E31038D9CBE}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="783" xr2:uid="{4CDCF8AC-F2BC-480F-9220-6E31038D9CBE}"/>
   </bookViews>
   <sheets>
     <sheet name="MC" sheetId="14" r:id="rId1"/>
@@ -21,8 +21,6 @@
     <sheet name="stringybark bulk density" sheetId="33" r:id="rId6"/>
     <sheet name="candle bark density (raw)" sheetId="36" r:id="rId7"/>
     <sheet name="candle bark density" sheetId="35" r:id="rId8"/>
-    <sheet name="Sheet2" sheetId="39" r:id="rId9"/>
-    <sheet name="Sheet1" sheetId="32" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'MC plot'!$B$10:$G$10</definedName>
@@ -46,7 +44,7 @@
     <definedName name="ExternalData_5" localSheetId="2" hidden="1">'twig bulk density (raw)'!$A$1:$G$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'stringybark bulk density'!$A$1:$H$55</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -339,17 +337,101 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="133">
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Tray</t>
+  </si>
+  <si>
+    <t>Empty tray</t>
+  </si>
+  <si>
+    <t>Fresh fuel (tray)</t>
+  </si>
+  <si>
+    <t>Fresh fuel (no tray)</t>
+  </si>
+  <si>
+    <t>Dried fuel (tray)</t>
+  </si>
+  <si>
+    <t>Dried fuel (no tray)</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Category ID</t>
+  </si>
+  <si>
+    <t>Eucalyptus</t>
+  </si>
+  <si>
+    <t>T1 (leave)</t>
+  </si>
+  <si>
+    <t>C4 (leave)</t>
+  </si>
+  <si>
+    <t>T2S</t>
+  </si>
+  <si>
+    <t>C3 (0 - 5 mm)</t>
+  </si>
+  <si>
+    <t>T3S</t>
+  </si>
+  <si>
+    <t>C2 (5 - 10 mm)</t>
+  </si>
+  <si>
+    <t>T4S</t>
+  </si>
+  <si>
+    <t>C1 (10 - 20 mm)</t>
+  </si>
+  <si>
+    <t>T5 (leave)</t>
+  </si>
+  <si>
+    <t>T6S</t>
+  </si>
+  <si>
+    <t>T7S</t>
+  </si>
+  <si>
+    <t>T8S</t>
+  </si>
+  <si>
+    <t>T9 (leave)</t>
+  </si>
+  <si>
+    <t>T10S</t>
+  </si>
+  <si>
+    <t>T11S</t>
+  </si>
+  <si>
+    <t>T12S</t>
+  </si>
+  <si>
+    <t>Pine</t>
+  </si>
+  <si>
+    <t>Acacia</t>
+  </si>
+  <si>
+    <t>Total (without leave)</t>
+  </si>
+  <si>
+    <t>Total (leave)</t>
+  </si>
   <si>
     <t>File (ID)</t>
   </si>
   <si>
-    <t>Volume (mm³)</t>
-  </si>
-  <si>
-    <t>Surface Area (mm²)</t>
-  </si>
-  <si>
     <t>Length (mm)</t>
   </si>
   <si>
@@ -362,64 +444,88 @@
     <t>Mass (g)</t>
   </si>
   <si>
-    <t>Tray</t>
-  </si>
-  <si>
-    <t>T2S</t>
-  </si>
-  <si>
-    <t>T3S</t>
-  </si>
-  <si>
-    <t>T4S</t>
-  </si>
-  <si>
-    <t>T6S</t>
-  </si>
-  <si>
-    <t>T7S</t>
-  </si>
-  <si>
-    <t>T8S</t>
-  </si>
-  <si>
-    <t>T10S</t>
-  </si>
-  <si>
-    <t>T11S</t>
-  </si>
-  <si>
-    <t>T12S</t>
-  </si>
-  <si>
-    <t>T1 (leave)</t>
-  </si>
-  <si>
-    <t>T5 (leave)</t>
-  </si>
-  <si>
-    <t>T9 (leave)</t>
-  </si>
-  <si>
-    <t>Empty tray</t>
-  </si>
-  <si>
-    <t>Fresh fuel (no tray)</t>
-  </si>
-  <si>
-    <t>Fresh fuel (tray)</t>
-  </si>
-  <si>
-    <t>Dried fuel (tray)</t>
-  </si>
-  <si>
-    <t>Dried fuel (no tray)</t>
-  </si>
-  <si>
-    <t>Total (without leave)</t>
-  </si>
-  <si>
-    <t>Total (leave)</t>
+    <t>Acacia 1_mesh_1.ply</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Acacia 1_mesh_2.ply</t>
+  </si>
+  <si>
+    <t>Acacia 1_mesh_3.ply</t>
+  </si>
+  <si>
+    <t>Acacia 2_mesh_1.ply</t>
+  </si>
+  <si>
+    <t>Acacia 2_mesh_2.ply</t>
+  </si>
+  <si>
+    <t>Acacia 2_mesh_3.ply</t>
+  </si>
+  <si>
+    <t>Acacia 3_mesh_1.ply</t>
+  </si>
+  <si>
+    <t>Acacia 3_mesh_2.ply</t>
+  </si>
+  <si>
+    <t>Acacia 3_mesh_3.ply</t>
+  </si>
+  <si>
+    <t>Eucalyptus 1_mesh_1.ply</t>
+  </si>
+  <si>
+    <t>Eucalyptus 1_mesh_2.ply</t>
+  </si>
+  <si>
+    <t>Eucalyptus 1_mesh_3.ply</t>
+  </si>
+  <si>
+    <t>Eucalyptus 2_mesh_1.ply</t>
+  </si>
+  <si>
+    <t>Eucalyptus 2_mesh_2.ply</t>
+  </si>
+  <si>
+    <t>Eucalyptus 2_mesh_3.ply</t>
+  </si>
+  <si>
+    <t>Eucalyptus 3_mesh_1.ply</t>
+  </si>
+  <si>
+    <t>Eucalyptus 3_mesh_2.ply</t>
+  </si>
+  <si>
+    <t>Eucalyptus 3_mesh_3.ply</t>
+  </si>
+  <si>
+    <t>Pine 1_mesh_1.ply</t>
+  </si>
+  <si>
+    <t>Pine 1_mesh_2.ply</t>
+  </si>
+  <si>
+    <t>Pine 1_mesh_3.ply</t>
+  </si>
+  <si>
+    <t>Pine 2_mesh_1.ply</t>
+  </si>
+  <si>
+    <t>Pine 2_mesh_2.ply</t>
+  </si>
+  <si>
+    <t>Pine 2_mesh_3.ply</t>
+  </si>
+  <si>
+    <t>Pine 3_mesh_1.ply</t>
+  </si>
+  <si>
+    <t>Pine 3_mesh_2.ply</t>
+  </si>
+  <si>
+    <t>Pine 3_mesh_3.ply</t>
   </si>
   <si>
     <t>Volume (mm3)</t>
@@ -428,39 +534,6 @@
     <t>Surface Area (mm2)</t>
   </si>
   <si>
-    <t>Species</t>
-  </si>
-  <si>
-    <t>Eucalyptus</t>
-  </si>
-  <si>
-    <t>Pine</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Acacia</t>
-  </si>
-  <si>
-    <t>C1 (10 - 20 mm)</t>
-  </si>
-  <si>
-    <t>C2 (5 - 10 mm)</t>
-  </si>
-  <si>
-    <t>Category ID</t>
-  </si>
-  <si>
-    <t>C4 (leave)</t>
-  </si>
-  <si>
-    <t>C3 (0 - 5 mm)</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>T16S12_mesh.ply</t>
   </si>
   <si>
@@ -627,87 +700,6 @@
   </si>
   <si>
     <t>Dried mass (g)</t>
-  </si>
-  <si>
-    <t>Acacia 1_mesh_1.ply</t>
-  </si>
-  <si>
-    <t>Acacia 1_mesh_2.ply</t>
-  </si>
-  <si>
-    <t>Acacia 1_mesh_3.ply</t>
-  </si>
-  <si>
-    <t>Acacia 2_mesh_1.ply</t>
-  </si>
-  <si>
-    <t>Acacia 2_mesh_2.ply</t>
-  </si>
-  <si>
-    <t>Acacia 2_mesh_3.ply</t>
-  </si>
-  <si>
-    <t>Acacia 3_mesh_1.ply</t>
-  </si>
-  <si>
-    <t>Acacia 3_mesh_2.ply</t>
-  </si>
-  <si>
-    <t>Acacia 3_mesh_3.ply</t>
-  </si>
-  <si>
-    <t>Eucalyptus 1_mesh_1.ply</t>
-  </si>
-  <si>
-    <t>Eucalyptus 1_mesh_2.ply</t>
-  </si>
-  <si>
-    <t>Eucalyptus 1_mesh_3.ply</t>
-  </si>
-  <si>
-    <t>Eucalyptus 2_mesh_1.ply</t>
-  </si>
-  <si>
-    <t>Eucalyptus 2_mesh_2.ply</t>
-  </si>
-  <si>
-    <t>Eucalyptus 2_mesh_3.ply</t>
-  </si>
-  <si>
-    <t>Eucalyptus 3_mesh_1.ply</t>
-  </si>
-  <si>
-    <t>Eucalyptus 3_mesh_2.ply</t>
-  </si>
-  <si>
-    <t>Eucalyptus 3_mesh_3.ply</t>
-  </si>
-  <si>
-    <t>Pine 1_mesh_1.ply</t>
-  </si>
-  <si>
-    <t>Pine 1_mesh_2.ply</t>
-  </si>
-  <si>
-    <t>Pine 1_mesh_3.ply</t>
-  </si>
-  <si>
-    <t>Pine 2_mesh_1.ply</t>
-  </si>
-  <si>
-    <t>Pine 2_mesh_2.ply</t>
-  </si>
-  <si>
-    <t>Pine 2_mesh_3.ply</t>
-  </si>
-  <si>
-    <t>Pine 3_mesh_1.ply</t>
-  </si>
-  <si>
-    <t>Pine 3_mesh_2.ply</t>
-  </si>
-  <si>
-    <t>Pine 3_mesh_3.ply</t>
   </si>
   <si>
     <t>Curve 1_mesh.ply</t>
@@ -1073,11 +1065,45 @@
       <cx:axis id="0">
         <cx:catScaling gapWidth="1"/>
         <cx:tickLabels/>
+        <cx:txPr>
+          <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1200" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </cx:txPr>
       </cx:axis>
       <cx:axis id="1">
         <cx:valScaling/>
         <cx:majorGridlines/>
         <cx:tickLabels/>
+        <cx:txPr>
+          <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1200" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </cx:txPr>
       </cx:axis>
     </cx:plotArea>
   </cx:chart>
@@ -1688,8 +1714,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9065231" y="468133"/>
-              <a:ext cx="5364480" cy="2657475"/>
+              <a:off x="8986491" y="473213"/>
+              <a:ext cx="5283200" cy="2695575"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1708,8 +1734,8 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100"/>
-                <a:t>This chart isn't available in your version of Excel.
+                <a:rPr lang="en-GB" sz="1100"/>
+                <a:t>This chart isn’t available in your version of Excel.
 Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
               </a:r>
             </a:p>
@@ -1826,8 +1852,8 @@
   <autoFilter ref="A1:G28" xr:uid="{64199DDE-D259-4682-94D0-1589746EAC38}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{FAB5CD80-064A-4982-8F1F-777D01629667}" uniqueName="1" name="File (ID)" queryTableFieldId="1" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{DE6A2580-3F22-441A-81ED-E243BEF0B4A8}" uniqueName="2" name="Volume (mm³)" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{15EA3F6F-74DD-4C4E-97B7-FF3D5E6BE445}" uniqueName="3" name="Surface Area (mm²)" queryTableFieldId="3"/>
+    <tableColumn id="2" xr3:uid="{DE6A2580-3F22-441A-81ED-E243BEF0B4A8}" uniqueName="2" name="Volume (mm3)" queryTableFieldId="2"/>
+    <tableColumn id="3" xr3:uid="{15EA3F6F-74DD-4C4E-97B7-FF3D5E6BE445}" uniqueName="3" name="Surface Area (mm2)" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{BED65517-483D-4307-8E6F-9C895D7493FC}" uniqueName="4" name="Length (mm)" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{DD80B76D-AD51-4858-B92F-76EA0F117F73}" uniqueName="5" name="Width (mm)" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{1DDEE77B-DCEE-47BA-95F0-7041F3B50DD8}" uniqueName="6" name="Height (mm)" queryTableFieldId="6"/>
@@ -1898,8 +1924,8 @@
   <autoFilter ref="A1:G11" xr:uid="{E8A40A47-E717-4DDC-810A-C6E39B22EA79}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{9350E563-5F22-464B-B73B-AE7190C84F82}" uniqueName="1" name="File (ID)" queryTableFieldId="1" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{8F13EE6A-ADC1-4D33-A462-9C8B6A538965}" uniqueName="2" name="Volume (mm³)" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{C3DF2350-56E1-444A-A0D1-CE5D23EC8CC0}" uniqueName="3" name="Surface Area (mm²)" queryTableFieldId="3"/>
+    <tableColumn id="2" xr3:uid="{8F13EE6A-ADC1-4D33-A462-9C8B6A538965}" uniqueName="2" name="Volume (mm3)" queryTableFieldId="2"/>
+    <tableColumn id="3" xr3:uid="{C3DF2350-56E1-444A-A0D1-CE5D23EC8CC0}" uniqueName="3" name="Surface Area (mm2)" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{F4F2C61F-E64E-41DE-B696-F01E0CDA64AB}" uniqueName="4" name="Length (mm)" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{07B5FE79-BB81-46E7-BC9F-AC87FFE1B6FC}" uniqueName="5" name="Width (mm)" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{A371525C-D282-4365-A9A2-F632D26B761D}" uniqueName="6" name="Height (mm)" queryTableFieldId="6"/>
@@ -2244,50 +2270,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A7B73B-664C-4D63-983A-9B40C9E9FCBC}">
   <dimension ref="A1:I37"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="4" max="4" width="15.19921875" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="14.5" customWidth="1"/>
     <col min="7" max="7" width="16.5" customWidth="1"/>
     <col min="9" max="9" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
-      </c>
       <c r="I1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>138.63</v>
@@ -2311,13 +2337,13 @@
         <v>123.44786015672091</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="4"/>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>24.6</v>
@@ -2341,13 +2367,13 @@
         <v>85.50091911764703</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="4"/>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>24.94</v>
@@ -2371,13 +2397,13 @@
         <v>90.766609880749613</v>
       </c>
       <c r="I4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="4"/>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>45.6</v>
@@ -2401,10 +2427,10 @@
         <v>100.74288072637228</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="4"/>
       <c r="B6" t="s">
         <v>18</v>
@@ -2431,13 +2457,13 @@
         <v>113.68153943751322</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="4"/>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>24.28</v>
@@ -2461,13 +2487,13 @@
         <v>60.781187724192939</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="4"/>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C8">
         <v>24.65</v>
@@ -2491,13 +2517,13 @@
         <v>104.37158469945356</v>
       </c>
       <c r="I8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="4"/>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>45.52</v>
@@ -2521,13 +2547,13 @@
         <v>131.5463003987594</v>
       </c>
       <c r="I9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="4"/>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10">
         <v>138.38</v>
@@ -2551,13 +2577,13 @@
         <v>101.81801978433292</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="4"/>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C11">
         <v>24.76</v>
@@ -2581,13 +2607,13 @@
         <v>85.120412844036693</v>
       </c>
       <c r="I11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="4"/>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C12">
         <v>24.67</v>
@@ -2611,13 +2637,13 @@
         <v>93.000958772770858</v>
       </c>
       <c r="I12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" s="4"/>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C13">
         <v>44.64</v>
@@ -2641,15 +2667,15 @@
         <v>113.61720067453626</v>
       </c>
       <c r="I13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C14">
         <v>138.63</v>
@@ -2673,13 +2699,13 @@
         <v>134.82330668910387</v>
       </c>
       <c r="I14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" s="4"/>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>24.6</v>
@@ -2703,13 +2729,13 @@
         <v>111.44893111638956</v>
       </c>
       <c r="I15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="4"/>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>24.94</v>
@@ -2733,13 +2759,13 @@
         <v>112.00327734535027</v>
       </c>
       <c r="I16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="4"/>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C17">
         <v>45.6</v>
@@ -2763,10 +2789,10 @@
         <v>116.36363636363645</v>
       </c>
       <c r="I17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="4"/>
       <c r="B18" t="s">
         <v>18</v>
@@ -2793,13 +2819,13 @@
         <v>138.66841587405716</v>
       </c>
       <c r="I18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" s="4"/>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C19">
         <v>24.28</v>
@@ -2823,13 +2849,13 @@
         <v>106.77666470241603</v>
       </c>
       <c r="I19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="4"/>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C20">
         <v>24.65</v>
@@ -2853,13 +2879,13 @@
         <v>59.580291970802925</v>
       </c>
       <c r="I20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="4"/>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <v>45.52</v>
@@ -2883,13 +2909,13 @@
         <v>110.82317073170734</v>
       </c>
       <c r="I21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="4"/>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C22">
         <v>138.38</v>
@@ -2913,13 +2939,13 @@
         <v>139.69290291379517</v>
       </c>
       <c r="I22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23" s="4"/>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C23">
         <v>24.76</v>
@@ -2943,13 +2969,13 @@
         <v>121.56690140845076</v>
       </c>
       <c r="I23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="4"/>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C24">
         <v>24.67</v>
@@ -2973,13 +2999,13 @@
         <v>118.82223445239406</v>
       </c>
       <c r="I24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25" s="4"/>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C25">
         <v>44.64</v>
@@ -3003,15 +3029,15 @@
         <v>118.56878470080193</v>
       </c>
       <c r="I25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C26">
         <v>138.63</v>
@@ -3035,13 +3061,13 @@
         <v>109.59746182827683</v>
       </c>
       <c r="I26" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A27" s="4"/>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C27">
         <v>24.6</v>
@@ -3065,13 +3091,13 @@
         <v>89.414414414414409</v>
       </c>
       <c r="I27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28" s="4"/>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C28">
         <v>24.94</v>
@@ -3095,13 +3121,13 @@
         <v>84.168336673346715</v>
       </c>
       <c r="I28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A29" s="4"/>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>45.6</v>
@@ -3125,10 +3151,10 @@
         <v>102.25563909774439</v>
       </c>
       <c r="I29" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" s="4"/>
       <c r="B30" t="s">
         <v>18</v>
@@ -3155,13 +3181,13 @@
         <v>110.32258064516137</v>
       </c>
       <c r="I30" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A31" s="4"/>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C31">
         <v>24.28</v>
@@ -3185,13 +3211,13 @@
         <v>78.694516971279384</v>
       </c>
       <c r="I31" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A32" s="4"/>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C32">
         <v>24.65</v>
@@ -3215,13 +3241,13 @@
         <v>88.06598806598808</v>
       </c>
       <c r="I32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A33" s="4"/>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C33">
         <v>45.52</v>
@@ -3245,13 +3271,13 @@
         <v>97.515808491418284</v>
       </c>
       <c r="I33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A34" s="4"/>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C34">
         <v>138.38</v>
@@ -3275,13 +3301,13 @@
         <v>115.38572251007476</v>
       </c>
       <c r="I34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A35" s="4"/>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C35">
         <v>24.76</v>
@@ -3305,13 +3331,13 @@
         <v>97.795535960319697</v>
       </c>
       <c r="I35" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A36" s="4"/>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C36">
         <v>24.67</v>
@@ -3335,13 +3361,13 @@
         <v>96.966413867822311</v>
       </c>
       <c r="I36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A37" s="4"/>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C37">
         <v>44.64</v>
@@ -3365,7 +3391,7 @@
         <v>99.577067669172919</v>
       </c>
       <c r="I37" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3380,53 +3406,44 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551C8D67-D819-4786-A571-55412EDEB770}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF48A7A-28A1-49D8-8D61-E28599DFD9B4}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="15.19921875" customWidth="1"/>
-    <col min="3" max="3" width="13.796875" customWidth="1"/>
-    <col min="4" max="4" width="15.19921875" customWidth="1"/>
-    <col min="6" max="6" width="18.69921875" customWidth="1"/>
-    <col min="7" max="7" width="11.296875" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>100.74288072637228</v>
@@ -3447,7 +3464,7 @@
         <v>100.74288072637228</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="4"/>
       <c r="B3">
         <v>131.5463003987594</v>
@@ -3468,7 +3485,7 @@
         <v>131.5463003987594</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="4"/>
       <c r="B4">
         <v>113.61720067453626</v>
@@ -3489,7 +3506,7 @@
         <v>113.61720067453626</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="4"/>
       <c r="F5">
         <v>90.766609880749613</v>
@@ -3498,7 +3515,7 @@
         <v>90.766609880749613</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="4"/>
       <c r="F6">
         <v>104.37158469945356</v>
@@ -3507,7 +3524,7 @@
         <v>104.37158469945356</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="4"/>
       <c r="F7">
         <v>93.000958772770858</v>
@@ -3516,7 +3533,7 @@
         <v>93.000958772770858</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="4"/>
       <c r="F8">
         <v>85.50091911764703</v>
@@ -3525,7 +3542,7 @@
         <v>85.50091911764703</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="4"/>
       <c r="F9">
         <v>60.781187724192939</v>
@@ -3534,7 +3551,7 @@
         <v>60.781187724192939</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" s="4"/>
       <c r="F10">
         <v>85.120412844036693</v>
@@ -3543,27 +3560,27 @@
         <v>85.120412844036693</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="4"/>
       <c r="G11">
         <v>123.44786015672091</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" s="4"/>
       <c r="G12">
         <v>113.68153943751322</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A13" s="4"/>
       <c r="G13">
         <v>101.81801978433292</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>116.36363636363645</v>
@@ -3584,7 +3601,7 @@
         <v>116.36363636363645</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" s="4"/>
       <c r="B15">
         <v>110.82317073170734</v>
@@ -3605,7 +3622,7 @@
         <v>110.82317073170734</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" s="4"/>
       <c r="B16">
         <v>118.56878470080193</v>
@@ -3626,7 +3643,7 @@
         <v>118.56878470080193</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="4"/>
       <c r="F17">
         <v>112.00327734535027</v>
@@ -3635,7 +3652,7 @@
         <v>112.00327734535027</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="4"/>
       <c r="F18">
         <v>59.580291970802925</v>
@@ -3644,7 +3661,7 @@
         <v>59.580291970802925</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="4"/>
       <c r="F19">
         <v>118.82223445239406</v>
@@ -3653,7 +3670,7 @@
         <v>118.82223445239406</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="4"/>
       <c r="F20">
         <v>111.44893111638956</v>
@@ -3662,7 +3679,7 @@
         <v>111.44893111638956</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="4"/>
       <c r="F21">
         <v>106.77666470241603</v>
@@ -3671,7 +3688,7 @@
         <v>106.77666470241603</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="4"/>
       <c r="F22">
         <v>121.56690140845076</v>
@@ -3680,27 +3697,27 @@
         <v>121.56690140845076</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="4"/>
       <c r="G23">
         <v>134.82330668910387</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="4"/>
       <c r="G24">
         <v>138.66841587405716</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="4"/>
       <c r="G25">
         <v>139.69290291379517</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>102.25563909774439</v>
@@ -3721,7 +3738,7 @@
         <v>102.25563909774439</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="4"/>
       <c r="B27">
         <v>97.515808491418284</v>
@@ -3742,7 +3759,7 @@
         <v>97.515808491418284</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="4"/>
       <c r="B28">
         <v>99.577067669172919</v>
@@ -3763,7 +3780,7 @@
         <v>99.577067669172919</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="4"/>
       <c r="F29">
         <v>84.168336673346715</v>
@@ -3772,7 +3789,7 @@
         <v>84.168336673346715</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="4"/>
       <c r="F30">
         <v>88.06598806598808</v>
@@ -3781,7 +3798,7 @@
         <v>88.06598806598808</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="4"/>
       <c r="F31">
         <v>96.966413867822311</v>
@@ -3790,7 +3807,7 @@
         <v>96.966413867822311</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="4"/>
       <c r="F32">
         <v>89.414414414414409</v>
@@ -3799,7 +3816,7 @@
         <v>89.414414414414409</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="4"/>
       <c r="F33">
         <v>78.694516971279384</v>
@@ -3808,7 +3825,7 @@
         <v>78.694516971279384</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="4"/>
       <c r="F34">
         <v>97.795535960319697</v>
@@ -3817,19 +3834,19 @@
         <v>97.795535960319697</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="4"/>
       <c r="G35">
         <v>109.59746182827683</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="4"/>
       <c r="G36">
         <v>110.32258064516137</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="4"/>
       <c r="G37">
         <v>115.38572251007476</v>
@@ -3850,43 +3867,43 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222DF109-B2C8-4C3D-936F-E2C6004E4E70}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="B2">
         <v>1922.0440000000001</v>
@@ -3904,12 +3921,12 @@
         <v>40.176000000000002</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>8193.8709999999992</v>
@@ -3927,12 +3944,12 @@
         <v>49.624000000000002</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>458.00400000000002</v>
@@ -3950,12 +3967,12 @@
         <v>40.344999999999999</v>
       </c>
       <c r="G4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>99</v>
       </c>
       <c r="B5">
         <v>3481.1869999999999</v>
@@ -3973,12 +3990,12 @@
         <v>43.786000000000001</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>7116.1350000000002</v>
@@ -3996,12 +4013,12 @@
         <v>48.173000000000002</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>573.87099999999998</v>
@@ -4019,12 +4036,12 @@
         <v>44.331000000000003</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <v>711.40700000000004</v>
@@ -4042,12 +4059,12 @@
         <v>39.094000000000001</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="B9">
         <v>7380.6080000000002</v>
@@ -4065,12 +4082,12 @@
         <v>49.255000000000003</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="B10">
         <v>1646.374</v>
@@ -4088,12 +4105,12 @@
         <v>43.195</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <v>2574.4769999999999</v>
@@ -4111,12 +4128,12 @@
         <v>38.545999999999999</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>8138.8149999999996</v>
@@ -4134,12 +4151,12 @@
         <v>42.268000000000001</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>1270.671</v>
@@ -4157,12 +4174,12 @@
         <v>37.393000000000001</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>2525.1779999999999</v>
@@ -4180,12 +4197,12 @@
         <v>11.586</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>7462.067</v>
@@ -4203,12 +4220,12 @@
         <v>18.998000000000001</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>1303.4590000000001</v>
@@ -4226,12 +4243,12 @@
         <v>11.824999999999999</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="B17">
         <v>632.00199999999995</v>
@@ -4249,12 +4266,12 @@
         <v>40.411000000000001</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <v>2669.625</v>
@@ -4272,12 +4289,12 @@
         <v>43.77</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="B19">
         <v>9153.3490000000002</v>
@@ -4295,12 +4312,12 @@
         <v>49.753</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <v>3804.1930000000002</v>
@@ -4318,12 +4335,12 @@
         <v>39.328000000000003</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>8903.2489999999998</v>
@@ -4341,12 +4358,12 @@
         <v>43.893999999999998</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>1565.0440000000001</v>
@@ -4364,12 +4381,12 @@
         <v>38.011000000000003</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <v>1086.452</v>
@@ -4387,12 +4404,12 @@
         <v>21.138999999999999</v>
       </c>
       <c r="G23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <v>8158.7520000000004</v>
@@ -4410,12 +4427,12 @@
         <v>30.032</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="B25">
         <v>3399.9259999999999</v>
@@ -4433,12 +4450,12 @@
         <v>22.55</v>
       </c>
       <c r="G25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="B26">
         <v>2946.6190000000001</v>
@@ -4456,12 +4473,12 @@
         <v>46.243000000000002</v>
       </c>
       <c r="G26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="B27">
         <v>7851.1760000000004</v>
@@ -4479,12 +4496,12 @@
         <v>51.932000000000002</v>
       </c>
       <c r="G27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="B28">
         <v>916.44500000000005</v>
@@ -4502,7 +4519,7 @@
         <v>42.289000000000001</v>
       </c>
       <c r="G28" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -4516,43 +4533,42 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4307760-E021-43EA-AB84-65E25210A935}">
   <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B2">
         <v>12875.998</v>
@@ -4570,12 +4586,12 @@
         <v>68.825999999999993</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>28228.556</v>
@@ -4593,12 +4609,12 @@
         <v>54.447000000000003</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="B4">
         <v>23400.512999999999</v>
@@ -4616,12 +4632,12 @@
         <v>51.432000000000002</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B5">
         <v>10686.29</v>
@@ -4639,12 +4655,12 @@
         <v>73.459999999999994</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="B6">
         <v>7628.1570000000002</v>
@@ -4662,12 +4678,12 @@
         <v>47.216999999999999</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="B7">
         <v>5166.9430000000002</v>
@@ -4685,12 +4701,12 @@
         <v>53.749000000000002</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="B8">
         <v>20368.356</v>
@@ -4708,12 +4724,12 @@
         <v>45.98</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="B9">
         <v>14905.328</v>
@@ -4731,12 +4747,12 @@
         <v>53.331000000000003</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B10">
         <v>38453.661999999997</v>
@@ -4754,12 +4770,12 @@
         <v>59.244999999999997</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B11">
         <v>20589.888999999999</v>
@@ -4777,12 +4793,12 @@
         <v>58.000999999999998</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B12">
         <v>4347.4889999999996</v>
@@ -4800,12 +4816,12 @@
         <v>45.445</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="B13">
         <v>5745.9570000000003</v>
@@ -4823,12 +4839,12 @@
         <v>48.215000000000003</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B14">
         <v>13704.144</v>
@@ -4846,12 +4862,12 @@
         <v>50.726999999999997</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B15">
         <v>10831.43</v>
@@ -4869,12 +4885,12 @@
         <v>48.348999999999997</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B16">
         <v>26884.648000000001</v>
@@ -4892,12 +4908,12 @@
         <v>53.145000000000003</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B17">
         <v>18615.175999999999</v>
@@ -4915,12 +4931,12 @@
         <v>57.6</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B18">
         <v>13759.232</v>
@@ -4938,12 +4954,12 @@
         <v>70.704999999999998</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="B19">
         <v>28467.663</v>
@@ -4961,12 +4977,12 @@
         <v>79.271000000000001</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="B20">
         <v>24512.941999999999</v>
@@ -4984,12 +5000,12 @@
         <v>80.775000000000006</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="B21">
         <v>13999.976000000001</v>
@@ -5007,12 +5023,12 @@
         <v>51.271999999999998</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="B22">
         <v>16668.073</v>
@@ -5030,12 +5046,12 @@
         <v>58.792999999999999</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B23">
         <v>12052.906000000001</v>
@@ -5053,12 +5069,12 @@
         <v>57.075000000000003</v>
       </c>
       <c r="G23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B24">
         <v>9761.5849999999991</v>
@@ -5076,12 +5092,12 @@
         <v>72.25</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="B25">
         <v>18427.883000000002</v>
@@ -5099,12 +5115,12 @@
         <v>68.623000000000005</v>
       </c>
       <c r="G25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="B26">
         <v>12618.278</v>
@@ -5122,12 +5138,12 @@
         <v>52.823</v>
       </c>
       <c r="G26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="B27">
         <v>29033.727999999999</v>
@@ -5145,12 +5161,12 @@
         <v>51.094999999999999</v>
       </c>
       <c r="G27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="B28">
         <v>35526.703000000001</v>
@@ -5168,12 +5184,12 @@
         <v>85.697000000000003</v>
       </c>
       <c r="G28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="B29">
         <v>19198.474999999999</v>
@@ -5191,12 +5207,12 @@
         <v>87.546000000000006</v>
       </c>
       <c r="G29" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B30">
         <v>22944.891</v>
@@ -5214,12 +5230,12 @@
         <v>61.802999999999997</v>
       </c>
       <c r="G30" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="B31">
         <v>22539.867999999999</v>
@@ -5237,12 +5253,12 @@
         <v>42.545000000000002</v>
       </c>
       <c r="G31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="B32">
         <v>24706.092000000001</v>
@@ -5260,12 +5276,12 @@
         <v>59.877000000000002</v>
       </c>
       <c r="G32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="B33">
         <v>22414.137999999999</v>
@@ -5283,12 +5299,12 @@
         <v>52.277000000000001</v>
       </c>
       <c r="G33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B34">
         <v>20591.18</v>
@@ -5306,12 +5322,12 @@
         <v>60.682000000000002</v>
       </c>
       <c r="G34" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="B35">
         <v>22312.103999999999</v>
@@ -5329,12 +5345,12 @@
         <v>54.404000000000003</v>
       </c>
       <c r="G35" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="B36">
         <v>16294.244000000001</v>
@@ -5352,12 +5368,12 @@
         <v>52.195999999999998</v>
       </c>
       <c r="G36" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="B37">
         <v>33005.750999999997</v>
@@ -5375,12 +5391,12 @@
         <v>42.146999999999998</v>
       </c>
       <c r="G37" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="B38">
         <v>35198.993000000002</v>
@@ -5398,12 +5414,12 @@
         <v>65.328000000000003</v>
       </c>
       <c r="G38" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="B39">
         <v>28838.348999999998</v>
@@ -5421,12 +5437,12 @@
         <v>54.725000000000001</v>
       </c>
       <c r="G39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="B40">
         <v>31249.955000000002</v>
@@ -5444,12 +5460,12 @@
         <v>51.613</v>
       </c>
       <c r="G40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="B41">
         <v>35810.533000000003</v>
@@ -5467,12 +5483,12 @@
         <v>65.361999999999995</v>
       </c>
       <c r="G41" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B42">
         <v>17405.883999999998</v>
@@ -5490,12 +5506,12 @@
         <v>64.302000000000007</v>
       </c>
       <c r="G42" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="B43">
         <v>35516.811999999998</v>
@@ -5513,12 +5529,12 @@
         <v>58.433999999999997</v>
       </c>
       <c r="G43" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="B44">
         <v>25192.880000000001</v>
@@ -5536,12 +5552,12 @@
         <v>53.225000000000001</v>
       </c>
       <c r="G44" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="B45">
         <v>14238.907999999999</v>
@@ -5559,12 +5575,12 @@
         <v>52.155999999999999</v>
       </c>
       <c r="G45" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="B46">
         <v>38172.652000000002</v>
@@ -5582,12 +5598,12 @@
         <v>68.099000000000004</v>
       </c>
       <c r="G46" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="B47">
         <v>45086.351000000002</v>
@@ -5605,12 +5621,12 @@
         <v>59.542000000000002</v>
       </c>
       <c r="G47" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B48">
         <v>43618.112000000001</v>
@@ -5628,12 +5644,12 @@
         <v>65.820999999999998</v>
       </c>
       <c r="G48" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="B49">
         <v>13114.105</v>
@@ -5651,12 +5667,12 @@
         <v>60.793999999999997</v>
       </c>
       <c r="G49" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="B50">
         <v>27397.567999999999</v>
@@ -5674,12 +5690,12 @@
         <v>66.599000000000004</v>
       </c>
       <c r="G50" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="B51">
         <v>53898.63</v>
@@ -5697,12 +5713,12 @@
         <v>63.201999999999998</v>
       </c>
       <c r="G51" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="B52">
         <v>20609.096000000001</v>
@@ -5720,12 +5736,12 @@
         <v>61.323</v>
       </c>
       <c r="G52" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B53">
         <v>23870.208999999999</v>
@@ -5743,12 +5759,12 @@
         <v>57.369</v>
       </c>
       <c r="G53" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B54">
         <v>25242.499</v>
@@ -5766,12 +5782,12 @@
         <v>61.094999999999999</v>
       </c>
       <c r="G54" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="B55">
         <v>53500.813000000002</v>
@@ -5789,7 +5805,7 @@
         <v>80.748000000000005</v>
       </c>
       <c r="G55" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -5803,47 +5819,47 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4082685A-F265-4475-8723-37424D474B99}">
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.69921875" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
     <col min="8" max="8" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="H1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="B2">
         <v>458.00400000000002</v>
@@ -5868,9 +5884,9 @@
         <v>0.27872264811900294</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>1922.0440000000001</v>
@@ -5895,9 +5911,9 @@
         <v>1.0377214804284918</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>8193.8709999999992</v>
@@ -5922,9 +5938,9 @@
         <v>4.5859775600345225</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>573.87099999999998</v>
@@ -5949,9 +5965,9 @@
         <v>0.33304564146824389</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>3481.1869999999999</v>
@@ -5976,9 +5992,9 @@
         <v>1.8881047875310961</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>7116.1350000000002</v>
@@ -6003,9 +6019,9 @@
         <v>4.2021627659034371</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <v>711.40700000000004</v>
@@ -6030,9 +6046,9 @@
         <v>0.37213788901863226</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="B9">
         <v>1646.374</v>
@@ -6057,9 +6073,9 @@
         <v>0.89810631060567592</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="B10">
         <v>7380.6080000000002</v>
@@ -6084,9 +6100,9 @@
         <v>4.2001319997969233</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <v>1270.671</v>
@@ -6111,9 +6127,9 @@
         <v>0.65181347150259061</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>2574.4769999999999</v>
@@ -6138,9 +6154,9 @@
         <v>1.5077720207253886</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>8138.8149999999996</v>
@@ -6165,9 +6181,9 @@
         <v>4.2274611398963735</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>1303.4590000000001</v>
@@ -6192,9 +6208,9 @@
         <v>0.72227979274611387</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>2525.1779999999999</v>
@@ -6219,9 +6235,9 @@
         <v>1.471502590673575</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>7462.067</v>
@@ -6246,9 +6262,9 @@
         <v>4.1834196891191704</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="B17">
         <v>632.00199999999995</v>
@@ -6273,9 +6289,9 @@
         <v>0.37150259067357511</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <v>2669.625</v>
@@ -6300,9 +6316,9 @@
         <v>1.4917098445595853</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="B19">
         <v>9153.3490000000002</v>
@@ -6327,9 +6343,9 @@
         <v>5.0580310880829016</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <v>1565.0440000000001</v>
@@ -6354,9 +6370,9 @@
         <v>0.5641509433962264</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>3804.1930000000002</v>
@@ -6381,9 +6397,9 @@
         <v>1.5566037735849054</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>8903.2489999999998</v>
@@ -6408,9 +6424,9 @@
         <v>4.1358490566037736</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <v>1086.452</v>
@@ -6435,9 +6451,9 @@
         <v>0.455188679245283</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <v>3399.9259999999999</v>
@@ -6462,9 +6478,9 @@
         <v>1.4023584905660376</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="B25">
         <v>8158.7520000000004</v>
@@ -6489,9 +6505,9 @@
         <v>3.770754716981132</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="B26">
         <v>916.44500000000005</v>
@@ -6516,9 +6532,9 @@
         <v>0.33820754716981127</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="B27">
         <v>2946.6190000000001</v>
@@ -6543,9 +6559,9 @@
         <v>0.8344339622641509</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="B28">
         <v>7851.1760000000004</v>
@@ -6582,47 +6598,47 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{208DAE51-1F40-4B18-8456-B58B6287EC40}">
   <dimension ref="A1:H55"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27.5" customWidth="1"/>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.69921875" customWidth="1"/>
-    <col min="8" max="8" width="13.296875" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="H1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B2">
         <v>12875.998</v>
@@ -6646,9 +6662,9 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>28228.556</v>
@@ -6672,9 +6688,9 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="B4">
         <v>23400.512999999999</v>
@@ -6698,9 +6714,9 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B5">
         <v>10686.29</v>
@@ -6724,9 +6740,9 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="B6">
         <v>7628.1570000000002</v>
@@ -6750,9 +6766,9 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="B7">
         <v>5166.9430000000002</v>
@@ -6776,9 +6792,9 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="B8">
         <v>14905.328</v>
@@ -6802,9 +6818,9 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="B9">
         <v>20368.356</v>
@@ -6828,9 +6844,9 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B10">
         <v>38453.661999999997</v>
@@ -6854,9 +6870,9 @@
         <v>18.603000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B11">
         <v>20589.888999999999</v>
@@ -6880,9 +6896,9 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B12">
         <v>4347.4889999999996</v>
@@ -6906,9 +6922,9 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="B13">
         <v>5745.9570000000003</v>
@@ -6932,9 +6948,9 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B14">
         <v>13704.144</v>
@@ -6958,9 +6974,9 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B15">
         <v>10831.43</v>
@@ -6984,9 +7000,9 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B16">
         <v>26884.648000000001</v>
@@ -7010,9 +7026,9 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B17">
         <v>18615.175999999999</v>
@@ -7036,9 +7052,9 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B18">
         <v>13759.232</v>
@@ -7062,9 +7078,9 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="B19">
         <v>28467.663</v>
@@ -7088,9 +7104,9 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="B20">
         <v>24512.941999999999</v>
@@ -7114,9 +7130,9 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="B21">
         <v>13999.976000000001</v>
@@ -7140,9 +7156,9 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="B22">
         <v>16668.073</v>
@@ -7166,9 +7182,9 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B23">
         <v>12052.906000000001</v>
@@ -7192,9 +7208,9 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B24">
         <v>9761.5849999999991</v>
@@ -7218,9 +7234,9 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="B25">
         <v>35526.703000000001</v>
@@ -7244,9 +7260,9 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="B26">
         <v>18427.883000000002</v>
@@ -7270,9 +7286,9 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="B27">
         <v>12618.278</v>
@@ -7296,9 +7312,9 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="B28">
         <v>29033.727999999999</v>
@@ -7322,9 +7338,9 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="B29">
         <v>19198.474999999999</v>
@@ -7348,9 +7364,9 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B30">
         <v>22944.891</v>
@@ -7374,9 +7390,9 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="B31">
         <v>22539.867999999999</v>
@@ -7400,9 +7416,9 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="B32">
         <v>24706.092000000001</v>
@@ -7426,9 +7442,9 @@
         <v>12.51</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="B33">
         <v>22414.137999999999</v>
@@ -7452,9 +7468,9 @@
         <v>11.48</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B34">
         <v>20591.18</v>
@@ -7478,9 +7494,9 @@
         <v>10.56</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="B35">
         <v>22312.103999999999</v>
@@ -7504,9 +7520,9 @@
         <v>10.34</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="B36">
         <v>16294.244000000001</v>
@@ -7530,9 +7546,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="B37">
         <v>33005.750999999997</v>
@@ -7556,9 +7572,9 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="B38">
         <v>35198.993000000002</v>
@@ -7582,9 +7598,9 @@
         <v>17.93</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="B39">
         <v>28838.348999999998</v>
@@ -7608,9 +7624,9 @@
         <v>13.42</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="B40">
         <v>31249.955000000002</v>
@@ -7634,9 +7650,9 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="B41">
         <v>35810.533000000003</v>
@@ -7660,9 +7676,9 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B42">
         <v>17405.883999999998</v>
@@ -7686,9 +7702,9 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="B43">
         <v>35516.811999999998</v>
@@ -7712,9 +7728,9 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="B44">
         <v>25192.880000000001</v>
@@ -7738,9 +7754,9 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="B45">
         <v>14238.907999999999</v>
@@ -7764,9 +7780,9 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="B46">
         <v>38172.652000000002</v>
@@ -7790,9 +7806,9 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="B47">
         <v>53898.63</v>
@@ -7816,9 +7832,9 @@
         <v>11.64</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="B48">
         <v>45086.351000000002</v>
@@ -7842,9 +7858,9 @@
         <v>7.64</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B49">
         <v>43618.112000000001</v>
@@ -7868,9 +7884,9 @@
         <v>11.77</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="B50">
         <v>13114.105</v>
@@ -7894,9 +7910,9 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="B51">
         <v>27397.567999999999</v>
@@ -7920,9 +7936,9 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="B52">
         <v>20609.096000000001</v>
@@ -7946,9 +7962,9 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B53">
         <v>23870.208999999999</v>
@@ -7972,9 +7988,9 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B54">
         <v>25242.499</v>
@@ -7998,9 +8014,9 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="B55">
         <v>53500.813000000002</v>
@@ -8036,43 +8052,43 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B61FF26E-60B6-444E-85C6-27A62C9D79EA}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="15.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B2">
         <v>7053.2719999999999</v>
@@ -8090,12 +8106,12 @@
         <v>98.759</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B3">
         <v>9543.5720000000001</v>
@@ -8113,12 +8129,12 @@
         <v>91.581999999999994</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B4">
         <v>9641.0370000000003</v>
@@ -8136,12 +8152,12 @@
         <v>90.959000000000003</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B5">
         <v>6111.69</v>
@@ -8159,12 +8175,12 @@
         <v>103.30800000000001</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B6">
         <v>3515.0749999999998</v>
@@ -8182,12 +8198,12 @@
         <v>118.551</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B7">
         <v>5733.1229999999996</v>
@@ -8205,12 +8221,12 @@
         <v>118.17700000000001</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B8">
         <v>5027.7550000000001</v>
@@ -8228,12 +8244,12 @@
         <v>86.41</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B9">
         <v>2012.87</v>
@@ -8251,12 +8267,12 @@
         <v>116.157</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B10">
         <v>8393.2890000000007</v>
@@ -8274,12 +8290,12 @@
         <v>92.525000000000006</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B11">
         <v>4163.96</v>
@@ -8297,7 +8313,7 @@
         <v>114.47499999999999</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -8311,47 +8327,47 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3198541A-AE7F-4362-A5B0-1DC6B89DB5E3}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="15.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" customWidth="1"/>
-    <col min="8" max="8" width="10.296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+    <col min="8" max="8" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="H1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B2">
         <v>7053.2719999999999</v>
@@ -8375,9 +8391,9 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B3">
         <v>9543.5720000000001</v>
@@ -8401,9 +8417,9 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B4">
         <v>9641.0370000000003</v>
@@ -8427,9 +8443,9 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B5">
         <v>6111.69</v>
@@ -8453,9 +8469,9 @@
         <v>6.19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B6">
         <v>3515.0749999999998</v>
@@ -8479,9 +8495,9 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B7">
         <v>5733.1229999999996</v>
@@ -8505,9 +8521,9 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B8">
         <v>5027.7550000000001</v>
@@ -8531,9 +8547,9 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B9">
         <v>6458.08</v>
@@ -8557,9 +8573,9 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B10">
         <v>6059</v>
@@ -8571,9 +8587,9 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B11">
         <v>5111</v>
@@ -8585,9 +8601,9 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B12">
         <v>8393.2890000000007</v>
@@ -8611,9 +8627,9 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B13">
         <v>4163.96</v>
@@ -8643,15 +8659,6 @@
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B04826-3F00-45B0-9DD9-C06341681347}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
